--- a/数字（すうじ）.xlsx
+++ b/数字（すうじ）.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="287">
   <si>
     <t>一人</t>
   </si>
@@ -349,12 +349,30 @@
     <t>しっぱい</t>
   </si>
   <si>
+    <t>削減</t>
+  </si>
+  <si>
+    <t>さくげん</t>
+  </si>
+  <si>
+    <t>未満</t>
+  </si>
+  <si>
+    <t>みまん</t>
+  </si>
+  <si>
     <t>稼働</t>
   </si>
   <si>
     <t>かどう</t>
   </si>
   <si>
+    <t>接近</t>
+  </si>
+  <si>
+    <t>せっきん</t>
+  </si>
+  <si>
     <t>就業</t>
   </si>
   <si>
@@ -367,6 +385,15 @@
     <t>いじ</t>
   </si>
   <si>
+    <t>同一</t>
+  </si>
+  <si>
+    <t>どういつ</t>
+  </si>
+  <si>
+    <t>（相同，相等）</t>
+  </si>
+  <si>
     <t>基準</t>
   </si>
   <si>
@@ -545,6 +572,12 @@
   </si>
   <si>
     <t>げんかい</t>
+  </si>
+  <si>
+    <t>とかく</t>
+  </si>
+  <si>
+    <t>（许多）</t>
   </si>
   <si>
     <t>視聴</t>
@@ -989,7 +1022,7 @@
     <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="28">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1039,13 +1072,6 @@
       <color theme="1"/>
       <name val="等线"/>
       <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1496,148 +1522,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2022,7 +2048,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P35"/>
+  <dimension ref="A1:P36"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8.11111111111111" customWidth="1"/>
@@ -2352,50 +2378,77 @@
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="F13" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" t="s">
+        <v>99</v>
+      </c>
+      <c r="J13" t="s">
+        <v>100</v>
+      </c>
+      <c r="K13" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="J14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K14" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
+      </c>
+      <c r="J15" t="s">
+        <v>110</v>
+      </c>
+      <c r="K15" t="s">
+        <v>111</v>
+      </c>
+      <c r="L15" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>104</v>
+        <v>113</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>105</v>
+        <v>114</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:8">
@@ -2409,72 +2462,72 @@
         <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>112</v>
+        <v>121</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>117</v>
+        <v>126</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>124</v>
+        <v>133</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>14</v>
@@ -2486,15 +2539,15 @@
         <v>74</v>
       </c>
       <c r="H21" t="s">
-        <v>126</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>127</v>
+        <v>136</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>128</v>
+        <v>137</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>14</v>
@@ -2504,178 +2557,186 @@
     </row>
     <row r="23" ht="18" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>129</v>
+        <v>138</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>130</v>
+        <v>139</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>131</v>
+        <v>140</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>133</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>134</v>
+        <v>143</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:8">
       <c r="A25" s="6" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:8">
       <c r="A26" s="6" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>146</v>
+        <v>155</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>147</v>
+        <v>156</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:8">
       <c r="A27" s="6" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>149</v>
+        <v>158</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>150</v>
+        <v>159</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>151</v>
+        <v>160</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="H28" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="31" ht="18" spans="1:8">
+        <v>172</v>
+      </c>
+      <c r="F30" t="s">
+        <v>173</v>
+      </c>
+      <c r="H30" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B31" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
-      <c r="F31" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="G31" s="1" t="s">
-        <v>167</v>
-      </c>
     </row>
     <row r="32" ht="18" spans="1:8">
       <c r="F32" s="1" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" ht="18" spans="6:7">
       <c r="F33" s="1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
     </row>
     <row r="34" ht="18" spans="6:7">
       <c r="F34" s="1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
     </row>
     <row r="35" ht="18" spans="6:7">
       <c r="F35" s="1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" ht="18" spans="6:7">
+      <c r="F36" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G36" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -2695,54 +2756,54 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="8" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="8" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="B4" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
     </row>
   </sheetData>
@@ -2772,16 +2833,16 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
@@ -2789,16 +2850,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
@@ -2806,16 +2867,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
@@ -2823,17 +2884,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
@@ -2841,17 +2902,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
@@ -2859,17 +2920,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
@@ -2877,17 +2938,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
@@ -2895,17 +2956,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
@@ -2913,17 +2974,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -2932,17 +2993,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -2951,183 +3012,183 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="F12" s="1" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="F15" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="A28" s="6" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
     </row>
     <row r="29" ht="15.6" spans="1:4">
       <c r="A29" s="6" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="C29" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" s="6" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="D30" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="C31" s="7"/>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/数字（すうじ）.xlsx
+++ b/数字（すうじ）.xlsx
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="294">
   <si>
     <t>一人</t>
   </si>
@@ -241,6 +241,12 @@
     <t>とくべつ</t>
   </si>
   <si>
+    <t>累計</t>
+  </si>
+  <si>
+    <t>るいけい</t>
+  </si>
+  <si>
     <t>精</t>
   </si>
   <si>
@@ -406,6 +412,15 @@
     <t>かいふく</t>
   </si>
   <si>
+    <t>近似</t>
+  </si>
+  <si>
+    <t>きんじ</t>
+  </si>
+  <si>
+    <t>近似曲線｜きんじきょくせん</t>
+  </si>
+  <si>
     <t>変更</t>
   </si>
   <si>
@@ -584,6 +599,12 @@
   </si>
   <si>
     <t>しちょう</t>
+  </si>
+  <si>
+    <t>投票</t>
+  </si>
+  <si>
+    <t>ようひょう</t>
   </si>
   <si>
     <t>抑制</t>
@@ -2243,212 +2264,227 @@
       <c r="K7" s="1" t="s">
         <v>61</v>
       </c>
+      <c r="N7" t="s">
+        <v>62</v>
+      </c>
+      <c r="O7" t="s">
+        <v>63</v>
+      </c>
     </row>
     <row r="8" ht="18" spans="1:16">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="H8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:16">
       <c r="A9" s="1" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="10" ht="18" spans="1:16">
       <c r="A10" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J10" s="6" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="11" ht="18" spans="1:16">
       <c r="A11" s="1" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="12" ht="18" spans="1:16">
       <c r="A12" s="1" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="H12" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="J12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:16">
       <c r="A13" s="1" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F13" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G13" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J13" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="K13" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:16">
       <c r="A14" s="1" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>14</v>
       </c>
       <c r="J14" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K14" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:16">
       <c r="A15" s="1" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="J15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="K15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="L15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" ht="18" spans="1:16">
       <c r="A16" s="1" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>116</v>
+        <v>118</v>
+      </c>
+      <c r="J16" t="s">
+        <v>119</v>
+      </c>
+      <c r="K16" t="s">
+        <v>120</v>
+      </c>
+      <c r="L16" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:8">
@@ -2462,92 +2498,92 @@
         <v>52</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:8">
       <c r="A18" s="1" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:8">
       <c r="A19" s="1" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" ht="18" spans="1:8">
       <c r="A20" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:8">
       <c r="A21" s="1" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:8">
       <c r="A22" s="1" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>14</v>
@@ -2557,186 +2593,195 @@
     </row>
     <row r="23" ht="18" spans="1:8">
       <c r="A23" s="1" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>59</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:8">
       <c r="A24" s="1" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
     </row>
     <row r="25" ht="18" spans="1:8">
       <c r="A25" s="6" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:8">
       <c r="A26" s="6" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:8">
       <c r="A27" s="6" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:8">
       <c r="A28" s="1" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="H28" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" ht="18" spans="1:8">
       <c r="A29" s="1" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
       <c r="G29" s="6" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:8">
       <c r="A30" s="1" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="F30" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="H30" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="C31" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="32" ht="18" spans="1:8">
+      <c r="A32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B32" t="s">
+        <v>183</v>
+      </c>
+      <c r="C32" t="s">
+        <v>14</v>
+      </c>
       <c r="F32" s="1" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
     </row>
     <row r="33" ht="18" spans="6:7">
       <c r="F33" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
     </row>
     <row r="34" ht="18" spans="6:7">
       <c r="F34" s="1" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
     </row>
     <row r="35" ht="18" spans="6:7">
       <c r="F35" s="1" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
     </row>
     <row r="36" ht="18" spans="6:7">
       <c r="F36" s="1" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2756,54 +2801,54 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="8" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>188</v>
+        <v>195</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>189</v>
+        <v>196</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="8" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>193</v>
+        <v>200</v>
       </c>
       <c r="B4" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
     </row>
   </sheetData>
@@ -2833,16 +2878,16 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>203</v>
+        <v>210</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>204</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
@@ -2850,16 +2895,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>205</v>
+        <v>212</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>207</v>
+        <v>214</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>208</v>
+        <v>215</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
@@ -2867,16 +2912,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>209</v>
+        <v>216</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
@@ -2884,17 +2929,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>216</v>
+        <v>223</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
@@ -2902,17 +2947,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>220</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
@@ -2920,17 +2965,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>223</v>
+        <v>230</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" t="s">
-        <v>224</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
@@ -2938,17 +2983,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>226</v>
+        <v>233</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>227</v>
+        <v>234</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" t="s">
-        <v>228</v>
+        <v>235</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
@@ -2956,17 +3001,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>229</v>
+        <v>236</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>232</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
@@ -2974,17 +3019,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>235</v>
+        <v>242</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -2993,17 +3038,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>240</v>
+        <v>247</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -3012,183 +3057,183 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>241</v>
+        <v>248</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>242</v>
+        <v>249</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>243</v>
+        <v>250</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>244</v>
+        <v>251</v>
       </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="F12" s="1" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>246</v>
+        <v>253</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>247</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>248</v>
+        <v>255</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="F15" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>253</v>
+        <v>260</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>254</v>
+        <v>261</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>255</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>257</v>
+        <v>264</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>258</v>
+        <v>265</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>260</v>
+        <v>267</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>261</v>
+        <v>268</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>262</v>
+        <v>269</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>263</v>
+        <v>270</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>265</v>
+        <v>272</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>266</v>
+        <v>273</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>267</v>
+        <v>274</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>268</v>
+        <v>275</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>269</v>
+        <v>276</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>270</v>
+        <v>277</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="A28" s="6" t="s">
-        <v>271</v>
+        <v>278</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>272</v>
+        <v>279</v>
       </c>
     </row>
     <row r="29" ht="15.6" spans="1:4">
       <c r="A29" s="6" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="C29" t="s">
-        <v>275</v>
+        <v>282</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" s="6" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="D30" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>280</v>
+        <v>287</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>281</v>
+        <v>288</v>
       </c>
       <c r="C31" s="7"/>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>282</v>
+        <v>289</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>283</v>
+        <v>290</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>284</v>
+        <v>291</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>286</v>
+        <v>293</v>
       </c>
     </row>
   </sheetData>

--- a/数字（すうじ）.xlsx
+++ b/数字（すうじ）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="23040" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="18288" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="特殊「とくしゅ」" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="294">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="304">
   <si>
     <t>一人</t>
   </si>
@@ -601,12 +601,45 @@
     <t>しちょう</t>
   </si>
   <si>
+    <t>～弱</t>
+  </si>
+  <si>
+    <t>じゃく</t>
+  </si>
+  <si>
+    <t>（不到...)</t>
+  </si>
+  <si>
     <t>投票</t>
   </si>
   <si>
     <t>ようひょう</t>
   </si>
   <si>
+    <t>～上</t>
+  </si>
+  <si>
+    <t>じょう</t>
+  </si>
+  <si>
+    <t>（超过...）</t>
+  </si>
+  <si>
+    <t>値下り</t>
+  </si>
+  <si>
+    <t>ねさがり</t>
+  </si>
+  <si>
+    <t>～寄り</t>
+  </si>
+  <si>
+    <t>より</t>
+  </si>
+  <si>
+    <t>（接近...）</t>
+  </si>
+  <si>
     <t>抑制</t>
   </si>
   <si>
@@ -659,9 +692,6 @@
   </si>
   <si>
     <t>乗</t>
-  </si>
-  <si>
-    <t>じょう</t>
   </si>
   <si>
     <t>÷</t>
@@ -2069,7 +2099,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P36"/>
+  <dimension ref="A1:P39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="8.11111111111111" customWidth="1"/>
@@ -2734,54 +2764,94 @@
       <c r="C31" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="32" ht="18" spans="1:8">
+      <c r="F31" t="s">
+        <v>182</v>
+      </c>
+      <c r="G31" t="s">
+        <v>183</v>
+      </c>
+      <c r="H31" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
       <c r="A32" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="C32" t="s">
         <v>14</v>
       </c>
-      <c r="F32" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="G32" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="33" ht="18" spans="6:7">
-      <c r="F33" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="G33" s="1" t="s">
+      <c r="F32" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="34" ht="18" spans="6:7">
-      <c r="F34" s="1" t="s">
+      <c r="G32" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="H32" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="35" ht="18" spans="6:7">
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>190</v>
+      </c>
+      <c r="B33" t="s">
+        <v>191</v>
+      </c>
+      <c r="C33" t="s">
+        <v>14</v>
+      </c>
+      <c r="F33" t="s">
+        <v>192</v>
+      </c>
+      <c r="G33" t="s">
+        <v>193</v>
+      </c>
+      <c r="H33" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="35" ht="18" spans="1:8">
       <c r="F35" s="1" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="36" ht="18" spans="6:7">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="36" ht="18" spans="1:8">
       <c r="F36" s="1" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>193</v>
+        <v>198</v>
+      </c>
+    </row>
+    <row r="37" ht="18" spans="1:8">
+      <c r="F37" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="38" ht="18" spans="1:8">
+      <c r="F38" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G38" s="1" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="39" ht="18" spans="1:8">
+      <c r="F39" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>204</v>
       </c>
     </row>
   </sheetData>
@@ -2801,54 +2871,54 @@
   <sheetData>
     <row r="2" ht="18" spans="1:3">
       <c r="A2" s="8" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:3">
       <c r="A3" s="8" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:3">
       <c r="A4" s="8" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>202</v>
+        <v>188</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:3">
       <c r="A5" s="8" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>204</v>
+        <v>214</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:3">
       <c r="A7" s="1" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
     </row>
   </sheetData>
@@ -2878,16 +2948,16 @@
   <sheetData>
     <row r="1" ht="18" spans="1:10">
       <c r="A1" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" ht="18" spans="1:10">
@@ -2895,16 +2965,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="3" ht="18" spans="1:10">
@@ -2912,16 +2982,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" ht="18" spans="1:10">
@@ -2929,17 +2999,17 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="E4" s="1"/>
       <c r="F4" s="1" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
     </row>
     <row r="5" ht="18" spans="1:10">
@@ -2947,17 +3017,17 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="1" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" ht="18" spans="1:10">
@@ -2965,17 +3035,17 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="E6" s="1"/>
       <c r="F6" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" ht="18" spans="1:10">
@@ -2983,17 +3053,17 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="E7" s="1"/>
       <c r="F7" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" ht="18" spans="1:10">
@@ -3001,17 +3071,17 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="E8" s="1"/>
       <c r="F8" s="1" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" ht="18" spans="1:10">
@@ -3019,17 +3089,17 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="E9" s="1"/>
       <c r="F9" s="1" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="J9" s="1"/>
     </row>
@@ -3038,17 +3108,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="E10" s="1"/>
       <c r="F10" s="1" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="J10" s="1"/>
     </row>
@@ -3057,183 +3127,183 @@
         <v>10</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="J11" s="1"/>
     </row>
     <row r="12" ht="18" spans="1:10">
       <c r="F12" s="1" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
     </row>
     <row r="13" ht="18" spans="1:10">
       <c r="A13" s="1" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" ht="18" spans="1:10">
       <c r="A14" s="1" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="15" ht="18" spans="1:10">
       <c r="A15" s="1" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F15" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="17" ht="18" spans="1:4">
       <c r="A17" s="1" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="18" ht="18" spans="1:4">
       <c r="A18" s="1" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="19" ht="18" spans="1:4">
       <c r="A19" s="1" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
     </row>
     <row r="21" ht="18" spans="1:4">
       <c r="A21" s="1" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" ht="18" spans="1:4">
       <c r="A22" s="1" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="23" ht="18" spans="1:4">
       <c r="A23" s="1" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" ht="18" spans="1:4">
       <c r="A24" s="1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
     </row>
     <row r="26" ht="18" spans="1:4">
       <c r="A26" s="1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="27" ht="18" spans="1:4">
       <c r="A27" s="1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" ht="18" spans="1:4">
       <c r="A28" s="6" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" ht="15.6" spans="1:4">
       <c r="A29" s="6" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="C29" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="30" ht="18" spans="1:4">
       <c r="A30" s="6" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D30" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="31" ht="18" spans="1:4">
       <c r="A31" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="C31" s="7"/>
     </row>
     <row r="33" ht="18" spans="1:3">
       <c r="A33" s="1" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" ht="18" spans="1:3">
       <c r="A34" s="1" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/数字（すうじ）.xlsx
+++ b/数字（すうじ）.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView windowWidth="18288" windowHeight="9180" activeTab="1"/>
+    <workbookView windowWidth="22188" windowHeight="9180" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="特殊「とくしゅ」" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="304">
   <si>
     <t>一人</t>
   </si>
@@ -2814,6 +2814,17 @@
         <v>194</v>
       </c>
     </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>138</v>
+      </c>
+      <c r="B34" t="s">
+        <v>139</v>
+      </c>
+      <c r="C34" t="s">
+        <v>14</v>
+      </c>
+    </row>
     <row r="35" ht="18" spans="1:8">
       <c r="F35" s="1" t="s">
         <v>195</v>
